--- a/tests/fixtures/tableau-cs.xlsx
+++ b/tests/fixtures/tableau-cs.xlsx
@@ -497,9 +497,6 @@
           <t>ICPE</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Ouvrir</t>
@@ -507,7 +504,6 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>CS26-002_DELTA</t>
@@ -518,12 +514,6 @@
           <t>Client Delta</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
